--- a/DTY May26產銷260427-1400+500+30_clear.xlsx
+++ b/DTY May26產銷260427-1400+500+30_clear.xlsx
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>FD2F6FK1 like</t>
+          <t>FD2F6FX1 like</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       <c r="W52" s="4" t="inlineStr"/>
       <c r="X52" s="4" t="inlineStr">
         <is>
-          <t>2F6FK1 LIKE</t>
+          <t>2F6FX1 LIKE</t>
         </is>
       </c>
     </row>
